--- a/site/Entra-ID-Multi-Application-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Multi-Application-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Provisioning</t>
+          <t>PII Attributes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,63 +649,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJCAT93805J6DK3W3GNEC7VA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Provisioning</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHB1QD4MW5GZ39EJ1K3SQBGM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>App Group Assignment</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KH0WV80872D2612QFJY684S0</t>
+          <t>h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KH0WV80872D2612QFJY684S0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KH0TD0YN440QFMS1M2XSJAHQ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>h_01KJFB5PFXSNTX6S024R53HHRN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJFB5PFXSNTX6S024R53HHRN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Rule</t>
+          <t>Application Groups</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,41 +737,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>h_01KJFB8K8DV4GRQ616DQRAJPS5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJFB8K8DV4GRQ616DQRAJPS5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Business Groups</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJFB909KSYK22Z0F567BKM61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Define PII Attribute</t>
+          <t>Password Policy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KH0XEMMDM0CPH9AGQCV6Z4JH</t>
+          <t>h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KH0XEMMDM0CPH9AGQCV6Z4JH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KG2E4KGJMSJ2PV6WHEJTWY81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Notification Rule</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,151 +803,151 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHBC8P4ZC05SGZV72J835H58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
+          <t>h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KG2CNKQEEHJD2XAZ9GV147N5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHB7QNKW672YBK3HS5MW3MME</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Define PII Attribute</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01K3JDHSDXSJJHPRZMHT47QV8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KHBC8P4Z96NEQJ87YCV9BW5D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
+          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KG2E4KGHCD65P9P0PY3KY9QD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJF5TV04837DX6QYCD2B82D1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJF5TM3TZB354J38P2K139A3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#01K5V7T6T6MJ13XCZYCT1T59VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,34 +957,56 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KEVBSF1NCB75TGKYHG2Q3V98</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Email Notification Settings</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KG4JSB4MRYSX92ACQDWVBQ2T</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01KG4JSB4MRYSX92ACQDWVBQ2T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Multi-Application-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
